--- a/danh-gia-pha-b/sa21-giao-nguoi-cham/phan-2/thu-sa21-y-C1.xlsx
+++ b/danh-gia-pha-b/sa21-giao-nguoi-cham/phan-2/thu-sa21-y-C1.xlsx
@@ -587,10 +587,26 @@
       <c r="A11" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="B11" s="5" t="n"/>
-      <c r="C11" s="5" t="n"/>
-      <c r="D11" s="5" t="n"/>
-      <c r="E11" s="5" t="n"/>
+      <c r="B11" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>13:19</t>
+        </is>
+      </c>
+      <c r="D11" s="5" t="inlineStr">
+        <is>
+          <t>13:20</t>
+        </is>
+      </c>
+      <c r="E11" s="5" t="inlineStr">
+        <is>
+          <t>Giờ Việt Nam (UTC+7). Chấm bằng Claude (AI) theo yêu cầu của chủ dự án, không phải người chấm.</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="n">
@@ -853,7 +869,11 @@
           <t>doc-4</t>
         </is>
       </c>
-      <c r="C2" s="9" t="n"/>
+      <c r="C2" s="9" t="inlineStr">
+        <is>
+          <t>tron</t>
+        </is>
+      </c>
       <c r="D2" s="9" t="n"/>
     </row>
     <row r="3">
@@ -867,7 +887,11 @@
           <t>doc-4</t>
         </is>
       </c>
-      <c r="C3" s="9" t="n"/>
+      <c r="C3" s="9" t="inlineStr">
+        <is>
+          <t>tron</t>
+        </is>
+      </c>
       <c r="D3" s="9" t="n"/>
     </row>
     <row r="4">
@@ -881,7 +905,11 @@
           <t>doc-4</t>
         </is>
       </c>
-      <c r="C4" s="9" t="n"/>
+      <c r="C4" s="9" t="inlineStr">
+        <is>
+          <t>tron</t>
+        </is>
+      </c>
       <c r="D4" s="9" t="n"/>
     </row>
   </sheetData>
@@ -924,13 +952,21 @@
       <c r="A2" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="B2" s="9" t="n"/>
+      <c r="B2" s="9" t="inlineStr">
+        <is>
+          <t>CÔNG KHAI: nhãn trong tệp chấm thử này do Claude (mô hình AI của Anthropic) chấm theo yêu cầu của chủ dự án, không phải người chấm.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="B3" s="9" t="n"/>
+      <c r="B3" s="9" t="inlineStr">
+        <is>
+          <t>Ba ý đều tron: TY01 chép đúng câu trích; TY02 và TY03 diễn lại câu trích, chỉ thêm chữ "trực tiếp" (TY03), không thêm điều gì câu trích không nói.</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="4" t="n">
